--- a/assessment_forms/018_study_data_quality_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/018_study_data_quality_assessment_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>study_data_quality_form_1</t>
+          <t>study_title</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Study Data Quality Form 1</t>
+          <t>What is the study title?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>study_data_quality_form_2</t>
+          <t>researcher</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Review Date</t>
+          <t>Who is the researcher?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>study_data_quality_form_3</t>
+          <t>researcher_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Researcher Name</t>
+          <t>What is the researcher's name?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>study_data_quality_form_4</t>
+          <t>reviewer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reviewer Name</t>
+          <t>What is the reviewer's name?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>study_data_quality_form_5</t>
+          <t>review_duration</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>What is the review duration?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>study_data_quality_form_6</t>
+          <t>review_type</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Comment</t>
+          <t>What is the review type?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>study_data_quality_form_7</t>
+          <t>study_status</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Study Title</t>
+          <t>Is the study active or inactive?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>study_data_quality_form_8</t>
+          <t>study_status_value</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reviewer Role</t>
+          <t>What is the study status?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>study_data_quality_form_9</t>
+          <t>review_period</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Research Team</t>
+          <t>What is the review period?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>study_data_quality_form_10</t>
+          <t>reviewer_score</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reviewer Comments</t>
+          <t>What is the reviewer score?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>study_data_quality_form_11</t>
+          <t>study_type</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reviewer Contact</t>
+          <t>Is the study type "yes" or "no"?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>study_data_quality_form_12</t>
+          <t>review_type_value</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Reviewer Email</t>
+          <t>What is the review type value?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>study_data_quality_form_13</t>
+          <t>review_comments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reviewer Phone</t>
+          <t>What are the review comments?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>study_data_quality_form_14</t>
+          <t>study_id</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Researcher Name</t>
+          <t>What is the study ID?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>study_data_quality_form_15</t>
+          <t>review_period_value</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Study ID</t>
+          <t>Review Period Value</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>study_data_quality_form_16</t>
+          <t>reviewer_comments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Study Title</t>
+          <t>What are the reviewer comments?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>study_data_quality_form_17</t>
+          <t>reviewer_contact</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Review Period</t>
+          <t>What is the reviewer contact?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>study_data_quality_form_18</t>
+          <t>reviewer_email</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Reviewer Score</t>
+          <t>What is the reviewer email?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,159 +929,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>study_data_quality_form_19</t>
+          <t>reviewer_phone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Review Duration</t>
+          <t>What is the reviewer phone?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>study_data_quality_form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Study Status</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>study_data_quality_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Study Type</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>study_data_quality_form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Review Type</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>study_data_quality_form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>study_data_quality_form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Review Period</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>study_data_quality_form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Reviewer Comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +960,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +988,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>study_data_quality_form_5_choices</t>
+          <t>review_duration_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1005,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>study_data_quality_form_5_choices</t>
+          <t>review_duration_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +1022,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>study_data_quality_form_19_choices</t>
+          <t>review_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1039,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>study_data_quality_form_19_choices</t>
+          <t>review_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1056,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>study_data_quality_form_20_choices</t>
+          <t>study_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1073,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>study_data_quality_form_20_choices</t>
+          <t>study_status_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1090,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>study_data_quality_form_21_choices</t>
+          <t>study_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1107,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>study_data_quality_form_21_choices</t>
+          <t>study_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1254,40 +1116,6 @@
         </is>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>study_data_quality_form_22_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>study_data_quality_form_22_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
